--- a/artfynd/A 49269-2020 artfynd.xlsx
+++ b/artfynd/A 49269-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49269-2020 artfynd.xlsx
+++ b/artfynd/A 49269-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1247,6 +1247,282 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>ASC0006 Arlanda Fågelinventering 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121622404</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58213</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>668580</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6618180</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ASC0019g Groddjursinventering Arlanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121622377</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58211</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>668606</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6618188</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hördes spelande åkergroda</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>ASC0019g Groddjursinventering Arlanda</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 49269-2020 artfynd.xlsx
+++ b/artfynd/A 49269-2020 artfynd.xlsx
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121622404</v>
+        <v>121622377</v>
       </c>
       <c r="B7" t="n">
-        <v>58213</v>
+        <v>58211</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,36 +1268,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>208250</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1311,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668580</v>
+        <v>668606</v>
       </c>
       <c r="R7" t="n">
-        <v>6618180</v>
+        <v>6618188</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,22 +1342,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hördes spelande åkergroda</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,7 +1382,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1387,10 +1393,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121622377</v>
+        <v>121622404</v>
       </c>
       <c r="B8" t="n">
-        <v>58211</v>
+        <v>58213</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,37 +1409,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1447,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668606</v>
+        <v>668580</v>
       </c>
       <c r="R8" t="n">
-        <v>6618188</v>
+        <v>6618180</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1477,27 +1482,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hördes spelande åkergroda</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 49269-2020 artfynd.xlsx
+++ b/artfynd/A 49269-2020 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>121622377</v>
       </c>
       <c r="B7" t="n">
-        <v>58211</v>
+        <v>58214</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>121622404</v>
       </c>
       <c r="B8" t="n">
-        <v>58213</v>
+        <v>58216</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 49269-2020 artfynd.xlsx
+++ b/artfynd/A 49269-2020 artfynd.xlsx
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121622377</v>
+        <v>121622404</v>
       </c>
       <c r="B7" t="n">
-        <v>58214</v>
+        <v>58216</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,37 +1268,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1312,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668606</v>
+        <v>668580</v>
       </c>
       <c r="R7" t="n">
-        <v>6618188</v>
+        <v>6618180</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1342,27 +1341,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hördes spelande åkergroda</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1376,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1393,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121622404</v>
+        <v>121622377</v>
       </c>
       <c r="B8" t="n">
-        <v>58216</v>
+        <v>58214</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,36 +1403,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208249</v>
+        <v>208250</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1452,10 +1447,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668580</v>
+        <v>668606</v>
       </c>
       <c r="R8" t="n">
-        <v>6618180</v>
+        <v>6618188</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1482,22 +1477,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hördes spelande åkergroda</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 49269-2020 artfynd.xlsx
+++ b/artfynd/A 49269-2020 artfynd.xlsx
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121622404</v>
+        <v>121622377</v>
       </c>
       <c r="B7" t="n">
-        <v>58216</v>
+        <v>58214</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,36 +1268,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>208250</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1311,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668580</v>
+        <v>668606</v>
       </c>
       <c r="R7" t="n">
-        <v>6618180</v>
+        <v>6618188</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,22 +1342,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hördes spelande åkergroda</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,7 +1382,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1387,10 +1393,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121622377</v>
+        <v>121622404</v>
       </c>
       <c r="B8" t="n">
-        <v>58214</v>
+        <v>58216</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,37 +1409,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1447,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668606</v>
+        <v>668580</v>
       </c>
       <c r="R8" t="n">
-        <v>6618188</v>
+        <v>6618180</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1477,27 +1482,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hördes spelande åkergroda</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 49269-2020 artfynd.xlsx
+++ b/artfynd/A 49269-2020 artfynd.xlsx
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121622377</v>
+        <v>121622404</v>
       </c>
       <c r="B7" t="n">
-        <v>58214</v>
+        <v>58224</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,37 +1268,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1312,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668606</v>
+        <v>668580</v>
       </c>
       <c r="R7" t="n">
-        <v>6618188</v>
+        <v>6618180</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1342,27 +1341,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hördes spelande åkergroda</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1376,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1393,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121622404</v>
+        <v>121622377</v>
       </c>
       <c r="B8" t="n">
-        <v>58216</v>
+        <v>58222</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,36 +1403,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208249</v>
+        <v>208250</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1452,10 +1447,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668580</v>
+        <v>668606</v>
       </c>
       <c r="R8" t="n">
-        <v>6618180</v>
+        <v>6618188</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1482,22 +1477,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hördes spelande åkergroda</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
